--- a/TP5/EJ4/EJ4.xlsx
+++ b/TP5/EJ4/EJ4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Universidad\2026\Recuperacion de la Informacion\RI-JosueGaticaOdato\TP5\EJ4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAFBF96-E052-4244-A648-43ED03865855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F360977-6D91-4EA5-8C7A-EB8491AA1850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="33">
   <si>
     <t>Step</t>
   </si>
@@ -383,7 +383,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -402,6 +402,66 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -411,65 +471,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="255" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -908,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:M50"/>
+  <dimension ref="B2:M74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -921,12 +927,12 @@
       <c r="C2" s="5">
         <v>6</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -935,10 +941,10 @@
       <c r="C3" s="6">
         <v>0.5</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -948,15 +954,15 @@
         <f>(1-$C$3)/$C$2</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="K4" s="8" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="K4" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="10"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="30"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K5" s="1" t="s">
@@ -1089,30 +1095,30 @@
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="16">
+      <c r="B10" s="9">
         <v>2</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="9">
         <f xml:space="preserve"> $C$4 + $C$3 * SUM((D9/$M$7),(G9/$M$10),(H9/$M$11))</f>
         <v>0.20833333333333331</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="9">
         <f t="shared" ref="D10:D18" si="1" xml:space="preserve"> $C$4 + $C$3 * SUM((C9/$M$6))</f>
         <v>0.15277777777777776</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="9">
         <f t="shared" ref="E10:E18" si="2" xml:space="preserve"> $C$4 + $C$3 * SUM((D9/$M$7),(F9/$M$9))</f>
         <v>0.20138888888888887</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="9">
         <f t="shared" ref="F10:F18" si="3" xml:space="preserve"> $C$4 + $C$3 * SUM((D9/$M$7),(E9/$M$8))</f>
         <v>0.20138888888888887</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="9">
         <f t="shared" ref="G10:G18" si="4" xml:space="preserve"> $C$4</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="9">
         <f t="shared" ref="H10:H18" si="5" xml:space="preserve"> $C$4 + $C$3 * SUM((C9/$M$6))</f>
         <v>0.15277777777777776</v>
       </c>
@@ -1131,7 +1137,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="3">
-        <f t="shared" ref="C10:C18" si="6" xml:space="preserve"> $C$4 + $C$3 * SUM((D10/$M$7),(G10/$M$10),(H10/$M$11))</f>
+        <f t="shared" ref="C11:C17" si="6" xml:space="preserve"> $C$4 + $C$3 * SUM((D10/$M$7),(G10/$M$10),(H10/$M$11))</f>
         <v>0.2268518518518518</v>
       </c>
       <c r="D11" s="3">
@@ -1194,38 +1200,38 @@
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="16">
+      <c r="B13" s="9">
         <v>5</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="9">
         <f t="shared" si="6"/>
         <v>0.21836419753086417</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="9">
         <f t="shared" si="1"/>
         <v>0.13715277777777776</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="9">
         <f t="shared" si="2"/>
         <v>0.21199845679012347</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="9">
         <f t="shared" si="3"/>
         <v>0.21199845679012347</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="9">
         <f t="shared" si="4"/>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="9">
         <f t="shared" si="5"/>
         <v>0.13715277777777776</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="K13" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="L13" s="9"/>
-      <c r="M13" s="10"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="30"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
@@ -1258,10 +1264,10 @@
       <c r="K14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="L14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="M14" s="12"/>
+      <c r="M14" s="18"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
@@ -1294,10 +1300,10 @@
       <c r="K15" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="L15" s="14" t="s">
+      <c r="L15" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="M15" s="15"/>
+      <c r="M15" s="32"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
@@ -1330,10 +1336,10 @@
       <c r="K16" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L16" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="M16" s="15"/>
+      <c r="L16" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="M16" s="32"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
@@ -1366,64 +1372,64 @@
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="14" t="s">
+      <c r="L17" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="M17" s="15"/>
+      <c r="M17" s="32"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B18" s="16">
+      <c r="B18" s="9">
         <v>10</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="9">
         <f xml:space="preserve"> $C$4 + $C$3 * SUM((D17/$M$7),(G17/$M$10),(H17/$M$11))</f>
         <v>0.21666023662551437</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="9">
         <f t="shared" si="1"/>
         <v>0.13751178840877915</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="9">
         <f t="shared" si="2"/>
         <v>0.21249142661179693</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="9">
         <f t="shared" si="3"/>
         <v>0.21249142661179693</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="9">
         <f t="shared" si="4"/>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="9">
         <f t="shared" si="5"/>
         <v>0.13751178840877915</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L18" s="14" t="s">
+      <c r="L18" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="15"/>
+      <c r="M18" s="32"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L19" s="14" t="s">
+      <c r="L19" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="M19" s="15"/>
+      <c r="M19" s="32"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L20" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="M20" s="13"/>
+      <c r="L20" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="M20" s="14"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
@@ -1432,12 +1438,12 @@
       <c r="C21" s="5">
         <v>6</v>
       </c>
-      <c r="E21" s="29" t="s">
+      <c r="E21" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
@@ -1446,17 +1452,17 @@
       <c r="C22" s="6">
         <v>0.15</v>
       </c>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="K22" s="28" t="s">
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="K22" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="L22" s="28" t="s">
+      <c r="L22" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="M22" s="28" t="s">
+      <c r="M22" s="11" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1468,11 +1474,11 @@
         <f>(1-$C$22)/$C$21</f>
         <v>0.14166666666666666</v>
       </c>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="K23" s="27">
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="K23" s="10">
         <v>1</v>
       </c>
       <c r="L23" s="1" t="s">
@@ -1483,7 +1489,7 @@
       </c>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K24" s="27">
+      <c r="K24" s="10">
         <v>2</v>
       </c>
       <c r="L24" s="1" t="s">
@@ -1494,7 +1500,7 @@
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K25" s="27">
+      <c r="K25" s="10">
         <v>3</v>
       </c>
       <c r="L25" s="1" t="s">
@@ -1526,7 +1532,7 @@
       <c r="H26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K26" s="27">
+      <c r="K26" s="10">
         <v>4</v>
       </c>
       <c r="L26" s="1" t="s">
@@ -1564,7 +1570,7 @@
         <f t="shared" si="7"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="K27" s="27">
+      <c r="K27" s="10">
         <v>5</v>
       </c>
       <c r="L27" s="1" t="s">
@@ -1602,7 +1608,7 @@
         <f xml:space="preserve"> $C$23 + $C$22 * SUM((C27/$M$6))</f>
         <v>0.15416666666666667</v>
       </c>
-      <c r="K28" s="27">
+      <c r="K28" s="10">
         <v>6</v>
       </c>
       <c r="L28" s="1" t="s">
@@ -1613,31 +1619,31 @@
       </c>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B29" s="16">
+      <c r="B29" s="9">
         <v>2</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="9">
         <f t="shared" ref="C29:C37" si="8" xml:space="preserve"> $C$23 + $C$22 * SUM((D28/$M$7),(G28/$M$10),(H28/$M$11))</f>
         <v>0.19374999999999998</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="9">
         <f t="shared" ref="D29:D37" si="9" xml:space="preserve"> $C$23 + $C$22 * SUM((C28/$M$6))</f>
         <v>0.15666666666666665</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="9">
         <f t="shared" ref="E29:E37" si="10" xml:space="preserve"> $C$23 + $C$22 * SUM((D28/$M$7),(F28/$M$9))</f>
         <v>0.175625</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="9">
         <f t="shared" ref="F29:F37" si="11" xml:space="preserve"> $C$23 + $C$22 * SUM((D28/$M$7),(E28/$M$8))</f>
         <v>0.175625</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="9">
         <f t="shared" ref="G29:G37" si="12" xml:space="preserve"> $C$23</f>
         <v>0.14166666666666666</v>
       </c>
-      <c r="H29" s="16">
-        <f t="shared" ref="H29:H37" si="13" xml:space="preserve"> $C$23 + $C$22 * SUM((C28/$M$6))</f>
+      <c r="H29" s="9">
+        <f t="shared" ref="H29:I37" si="13" xml:space="preserve"> $C$23 + $C$22 * SUM((C28/$M$6))</f>
         <v>0.15666666666666665</v>
       </c>
     </row>
@@ -1700,34 +1706,34 @@
       </c>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B32" s="16">
+      <c r="B32" s="9">
         <v>5</v>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="9">
         <f t="shared" si="8"/>
         <v>0.19416375</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="9">
         <f t="shared" si="9"/>
         <v>0.15622838541666667</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="9">
         <f t="shared" si="10"/>
         <v>0.17585640624999999</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="9">
         <f t="shared" si="11"/>
         <v>0.17585640624999999</v>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="9">
         <f t="shared" si="12"/>
         <v>0.14166666666666666</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="9">
         <f t="shared" si="13"/>
         <v>0.15622838541666667</v>
       </c>
-      <c r="I32" s="30"/>
+      <c r="I32" s="12"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="3">
@@ -1757,7 +1763,7 @@
         <f t="shared" si="13"/>
         <v>0.15622894791666667</v>
       </c>
-      <c r="I33" s="30"/>
+      <c r="I33" s="12"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="3">
@@ -1787,7 +1793,7 @@
         <f t="shared" si="13"/>
         <v>0.15622884244791665</v>
       </c>
-      <c r="I34" s="30"/>
+      <c r="I34" s="12"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="3">
@@ -1817,7 +1823,7 @@
         <f t="shared" si="13"/>
         <v>0.15622885088541666</v>
       </c>
-      <c r="I35" s="30"/>
+      <c r="I35" s="12"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="3">
@@ -1847,87 +1853,87 @@
         <f t="shared" si="13"/>
         <v>0.1562288493033854</v>
       </c>
-      <c r="I36" s="30"/>
+      <c r="I36" s="12"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="16">
+      <c r="B37" s="9">
         <v>10</v>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="9">
         <f t="shared" si="8"/>
         <v>0.19416243652734375</v>
       </c>
-      <c r="D37" s="16">
+      <c r="D37" s="9">
         <f t="shared" si="9"/>
         <v>0.15622884942994791</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="9">
         <f t="shared" si="10"/>
         <v>0.17585659897304687</v>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="9">
         <f t="shared" si="11"/>
         <v>0.17585659897304687</v>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="9">
         <f t="shared" si="12"/>
         <v>0.14166666666666666</v>
       </c>
-      <c r="H37" s="16">
+      <c r="H37" s="9">
         <f t="shared" si="13"/>
         <v>0.15622884942994791</v>
       </c>
-      <c r="I37" s="30"/>
+      <c r="I37" s="12"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="25" t="s">
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="H40" s="25">
-        <v>0.5</v>
+      <c r="H40" s="26">
+        <v>0.2</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="22"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
       <c r="J41" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="19"/>
-      <c r="D43" s="12"/>
-      <c r="F43" s="18" t="s">
+      <c r="C43" s="17"/>
+      <c r="D43" s="18"/>
+      <c r="F43" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
@@ -1954,11 +1960,11 @@
         <v>1</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D45" s="3">
-        <f>$H$40*$M$23 + (1-$H$40)*$G$18</f>
-        <v>2.5283666666666664</v>
+        <f>$H$40*$M$24 + (1-$H$40)*$E$18</f>
+        <v>1.1334531412894377</v>
       </c>
       <c r="F45" s="1">
         <v>1</v>
@@ -1968,7 +1974,7 @@
       </c>
       <c r="H45" s="3">
         <f>$H$40*$M$23 + (1-$H$40)*$G$37</f>
-        <v>2.5575333333333332</v>
+        <v>1.1080133333333333</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
@@ -1976,11 +1982,11 @@
         <v>2</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D46" s="3">
-        <f>$H$40*$M$24 + (1-$H$40)*$E$18</f>
-        <v>2.5148957133058985</v>
+        <f>$H$40*$M$23 + (1-$H$40)*$G$18</f>
+        <v>1.0613466666666667</v>
       </c>
       <c r="F46" s="1">
         <v>2</v>
@@ -1990,7 +1996,7 @@
       </c>
       <c r="H46" s="3">
         <f>$H$40*$M$24 + (1-$H$40)*$E$37</f>
-        <v>2.4965782994865235</v>
+        <v>1.1041452791784376</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
@@ -2002,7 +2008,7 @@
       </c>
       <c r="D47" s="3">
         <f>$H$40*$M$25 + (1-$H$40)*$C$18</f>
-        <v>1.3891801183127572</v>
+        <v>0.68566818930041151</v>
       </c>
       <c r="F47" s="1">
         <v>3</v>
@@ -2012,7 +2018,7 @@
       </c>
       <c r="H47" s="3">
         <f>$H$40*$M$25 + (1-$H$40)*$C$37</f>
-        <v>1.3779312182636718</v>
+        <v>0.66766994922187506</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.25">
@@ -2024,7 +2030,7 @@
       </c>
       <c r="D48" s="3">
         <f>$H$40*$M$26 + (1-$H$40)*$D$18</f>
-        <v>1.0742558942043896</v>
+        <v>0.51220943072702341</v>
       </c>
       <c r="F48" s="1">
         <v>4</v>
@@ -2034,7 +2040,7 @@
       </c>
       <c r="H48" s="3">
         <f>$H$40*$M$26 + (1-$H$40)*$D$37</f>
-        <v>1.0836144247149739</v>
+        <v>0.52718307954395838</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
@@ -2046,7 +2052,7 @@
       </c>
       <c r="D49" s="3">
         <f>$H$40*$M$27 + (1-$H$40)*$F$18</f>
-        <v>0.55309571330589846</v>
+        <v>0.34873314128943755</v>
       </c>
       <c r="F49" s="1">
         <v>5</v>
@@ -2056,7 +2062,7 @@
       </c>
       <c r="H49" s="3">
         <f>$H$40*$M$27 + (1-$H$40)*$F$37</f>
-        <v>0.53477829948652345</v>
+        <v>0.31942527917843755</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.25">
@@ -2068,7 +2074,7 @@
       </c>
       <c r="D50" s="3">
         <f>$H$40*$M$28 + (1-$H$40)*$H$18</f>
-        <v>6.8755894204389573E-2</v>
+        <v>0.11000943072702332</v>
       </c>
       <c r="F50" s="1">
         <v>6</v>
@@ -2078,14 +2084,401 @@
       </c>
       <c r="H50" s="3">
         <f>$H$40*$M$28 + (1-$H$40)*$H$37</f>
+        <v>0.12498307954395833</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B52" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="H52" s="26">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B53" s="23"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B55" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="17"/>
+      <c r="D55" s="18"/>
+      <c r="F55" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G55" s="19"/>
+      <c r="H55" s="19"/>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B56" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B57" s="7">
+        <v>1</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="8">
+        <f>$H$52*$M$23 + (1-$H$52)*$G$18</f>
+        <v>2.5283666666666664</v>
+      </c>
+      <c r="F57" s="7">
+        <v>1</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="8">
+        <f>$H$52*$M$23 + (1-$H$52)*$G$37</f>
+        <v>2.5575333333333332</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B58" s="7">
+        <v>2</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="8">
+        <f>$H$52*$M$24 + (1-$H$52)*$E$18</f>
+        <v>2.5148957133058985</v>
+      </c>
+      <c r="F58" s="7">
+        <v>2</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="8">
+        <f>$H$52*$M$24 + (1-$H$52)*$E$37</f>
+        <v>2.4965782994865235</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B59" s="7">
+        <v>3</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D59" s="8">
+        <f>$H$52*$M$25 + (1-$H$52)*$C$18</f>
+        <v>1.3891801183127572</v>
+      </c>
+      <c r="F59" s="7">
+        <v>3</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H59" s="8">
+        <f>$H$52*$M$25 + (1-$H$52)*$C$37</f>
+        <v>1.3779312182636718</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B60" s="7">
+        <v>4</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D60" s="8">
+        <f>$H$52*$M$26 + (1-$H$52)*$D$18</f>
+        <v>1.0742558942043896</v>
+      </c>
+      <c r="F60" s="7">
+        <v>4</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H60" s="8">
+        <f>$H$52*$M$26 + (1-$H$52)*$D$37</f>
+        <v>1.0836144247149739</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B61" s="7">
+        <v>5</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" s="8">
+        <f>$H$52*$M$27 + (1-$H$52)*$F$18</f>
+        <v>0.55309571330589846</v>
+      </c>
+      <c r="F61" s="7">
+        <v>5</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H61" s="8">
+        <f>$H$52*$M$27 + (1-$H$52)*$F$37</f>
+        <v>0.53477829948652345</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B62" s="7">
+        <v>6</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="8">
+        <f>$H$52*$M$28 + (1-$H$52)*$H$18</f>
+        <v>6.8755894204389573E-2</v>
+      </c>
+      <c r="F62" s="7">
+        <v>6</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H62" s="8">
+        <f>$H$52*$M$28 + (1-$H$52)*$H$37</f>
         <v>7.8114424714973957E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B64" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="H64" s="26">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B65" s="23"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="25"/>
+      <c r="G65" s="27"/>
+      <c r="H65" s="27"/>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B67" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="17"/>
+      <c r="D67" s="18"/>
+      <c r="F67" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G67" s="19"/>
+      <c r="H67" s="19"/>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B68" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B69" s="7">
+        <v>1</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" s="8">
+        <f>$H$64*$M$23 + (1-$H$64)*$G$18</f>
+        <v>4.4843933333333341</v>
+      </c>
+      <c r="F69" s="7">
+        <v>1</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H69" s="8">
+        <f>$H$64*$M$23 + (1-$H$64)*$G$37</f>
+        <v>4.4902266666666675</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B70" s="7">
+        <v>2</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="8">
+        <f>$H$64*$M$24 + (1-$H$64)*$E$18</f>
+        <v>4.3568191426611804</v>
+      </c>
+      <c r="F70" s="7">
+        <v>2</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H70" s="8">
+        <f>$H$64*$M$24 + (1-$H$64)*$E$37</f>
+        <v>4.3531556598973049</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B71" s="7">
+        <v>3</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D71" s="8">
+        <f>$H$64*$M$25 + (1-$H$64)*$C$18</f>
+        <v>2.3271960236625513</v>
+      </c>
+      <c r="F71" s="7">
+        <v>3</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H71" s="8">
+        <f>$H$64*$M$25 + (1-$H$64)*$C$37</f>
+        <v>2.3249462436527346</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B72" s="7">
+        <v>4</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" s="8">
+        <f>$H$64*$M$26 + (1-$H$64)*$D$18</f>
+        <v>1.823651178840878</v>
+      </c>
+      <c r="F72" s="7">
+        <v>4</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H72" s="8">
+        <f>$H$64*$M$26 + (1-$H$64)*$D$37</f>
+        <v>1.8255228849429948</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B73" s="7">
+        <v>5</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D73" s="8">
+        <f>$H$64*$M$27 + (1-$H$64)*$F$18</f>
+        <v>0.82557914266117982</v>
+      </c>
+      <c r="F73" s="7">
+        <v>5</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H73" s="8">
+        <f>$H$64*$M$27 + (1-$H$64)*$F$37</f>
+        <v>0.82191565989730475</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B74" s="7">
+        <v>6</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" s="8">
+        <f>$H$64*$M$28 + (1-$H$64)*$H$18</f>
+        <v>1.3751178840877912E-2</v>
+      </c>
+      <c r="F74" s="7">
+        <v>6</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H74" s="8">
+        <f>$H$64*$M$28 + (1-$H$64)*$H$37</f>
+        <v>1.5622884942994788E-2</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G45:H50">
     <sortCondition descending="1" ref="H45:H50"/>
   </sortState>
-  <mergeCells count="17">
+  <mergeCells count="27">
+    <mergeCell ref="B64:F65"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="H64:H65"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="B52:F53"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="F55:H55"/>
     <mergeCell ref="E2:H4"/>
     <mergeCell ref="L20:M20"/>
     <mergeCell ref="B39:H39"/>
@@ -2102,7 +2495,6 @@
     <mergeCell ref="L16:M16"/>
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L19:M19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
